--- a/data_lake/datos_diarios_preliminares/dt=2026-09-11/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-11/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12AE51B-4911-43ED-BBE7-5D6C13263CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75585442-9236-4F29-B220-FE86C783A461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$A$4:$AS$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="159" width="32.42578125" style="50" customWidth="1"/>
-    <col min="160" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="160" width="32.42578125" style="50" customWidth="1"/>
+    <col min="161" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6665,7 +6664,9 @@
       <c r="S5" s="56">
         <v>30.2</v>
       </c>
-      <c r="T5" s="56"/>
+      <c r="T5" s="56">
+        <v>30</v>
+      </c>
       <c r="U5" s="56"/>
       <c r="V5" s="56"/>
       <c r="W5" s="56"/>
@@ -6689,7 +6690,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6762,7 +6763,9 @@
       <c r="S6" s="56">
         <v>30.5</v>
       </c>
-      <c r="T6" s="56"/>
+      <c r="T6" s="56">
+        <v>30.1</v>
+      </c>
       <c r="U6" s="56"/>
       <c r="V6" s="56"/>
       <c r="W6" s="56"/>
@@ -6786,7 +6789,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6859,7 +6862,9 @@
       <c r="S7" s="56">
         <v>32.799999999999997</v>
       </c>
-      <c r="T7" s="56"/>
+      <c r="T7" s="56">
+        <v>30.7</v>
+      </c>
       <c r="U7" s="56"/>
       <c r="V7" s="56"/>
       <c r="W7" s="56"/>
@@ -6883,7 +6888,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6956,7 +6961,9 @@
       <c r="S8" s="56">
         <v>31.3</v>
       </c>
-      <c r="T8" s="56"/>
+      <c r="T8" s="56">
+        <v>31.2</v>
+      </c>
       <c r="U8" s="56"/>
       <c r="V8" s="56"/>
       <c r="W8" s="56"/>
@@ -6980,7 +6987,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7053,7 +7060,9 @@
       <c r="S9" s="56">
         <v>31</v>
       </c>
-      <c r="T9" s="56"/>
+      <c r="T9" s="56">
+        <v>30.8</v>
+      </c>
       <c r="U9" s="56"/>
       <c r="V9" s="56"/>
       <c r="W9" s="56"/>
@@ -7077,7 +7086,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7150,7 +7159,9 @@
       <c r="S10" s="56">
         <v>32.299999999999997</v>
       </c>
-      <c r="T10" s="56"/>
+      <c r="T10" s="56">
+        <v>32.5</v>
+      </c>
       <c r="U10" s="56"/>
       <c r="V10" s="56"/>
       <c r="W10" s="56"/>
@@ -7174,7 +7185,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7247,7 +7258,9 @@
       <c r="S11" s="56">
         <v>34.5</v>
       </c>
-      <c r="T11" s="56"/>
+      <c r="T11" s="56">
+        <v>33.200000000000003</v>
+      </c>
       <c r="U11" s="56"/>
       <c r="V11" s="56"/>
       <c r="W11" s="56"/>
@@ -7271,7 +7284,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7344,7 +7357,9 @@
       <c r="S12" s="56">
         <v>30.3</v>
       </c>
-      <c r="T12" s="56"/>
+      <c r="T12" s="56">
+        <v>28.3</v>
+      </c>
       <c r="U12" s="56"/>
       <c r="V12" s="56"/>
       <c r="W12" s="56"/>
@@ -7368,7 +7383,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7441,7 +7456,9 @@
       <c r="S13" s="56">
         <v>32.9</v>
       </c>
-      <c r="T13" s="56"/>
+      <c r="T13" s="56">
+        <v>31.3</v>
+      </c>
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
       <c r="W13" s="56"/>
@@ -7465,7 +7482,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7538,7 +7555,9 @@
       <c r="S14" s="56">
         <v>24.8</v>
       </c>
-      <c r="T14" s="56"/>
+      <c r="T14" s="56">
+        <v>24.3</v>
+      </c>
       <c r="U14" s="56"/>
       <c r="V14" s="56"/>
       <c r="W14" s="56"/>
@@ -7562,7 +7581,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7635,7 +7654,9 @@
       <c r="S15" s="56">
         <v>31.9</v>
       </c>
-      <c r="T15" s="56"/>
+      <c r="T15" s="56">
+        <v>30</v>
+      </c>
       <c r="U15" s="56"/>
       <c r="V15" s="56"/>
       <c r="W15" s="56"/>
@@ -7659,7 +7680,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7732,7 +7753,9 @@
       <c r="S16" s="56">
         <v>29.6</v>
       </c>
-      <c r="T16" s="56"/>
+      <c r="T16" s="56">
+        <v>28.3</v>
+      </c>
       <c r="U16" s="56"/>
       <c r="V16" s="56"/>
       <c r="W16" s="56"/>
@@ -7756,7 +7779,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7829,7 +7852,9 @@
       <c r="S17" s="56">
         <v>27.1</v>
       </c>
-      <c r="T17" s="56"/>
+      <c r="T17" s="56">
+        <v>26</v>
+      </c>
       <c r="U17" s="56"/>
       <c r="V17" s="56"/>
       <c r="W17" s="56"/>
@@ -7853,7 +7878,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7926,7 +7951,9 @@
       <c r="S18" s="56">
         <v>19.8</v>
       </c>
-      <c r="T18" s="56"/>
+      <c r="T18" s="56">
+        <v>19.8</v>
+      </c>
       <c r="U18" s="56"/>
       <c r="V18" s="56"/>
       <c r="W18" s="56"/>
@@ -7950,7 +7977,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8023,7 +8050,9 @@
       <c r="S19" s="56">
         <v>25.4</v>
       </c>
-      <c r="T19" s="56"/>
+      <c r="T19" s="56">
+        <v>25.9</v>
+      </c>
       <c r="U19" s="56"/>
       <c r="V19" s="56"/>
       <c r="W19" s="56"/>
@@ -8047,7 +8076,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8120,7 +8149,9 @@
       <c r="S20" s="56">
         <v>24.7</v>
       </c>
-      <c r="T20" s="56"/>
+      <c r="T20" s="56">
+        <v>25.3</v>
+      </c>
       <c r="U20" s="56"/>
       <c r="V20" s="56"/>
       <c r="W20" s="56"/>
@@ -8144,7 +8175,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8217,7 +8248,9 @@
       <c r="S21" s="56">
         <v>29.1</v>
       </c>
-      <c r="T21" s="56"/>
+      <c r="T21" s="56">
+        <v>29.7</v>
+      </c>
       <c r="U21" s="56"/>
       <c r="V21" s="56"/>
       <c r="W21" s="56"/>
@@ -8241,7 +8274,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8314,7 +8347,9 @@
       <c r="S22" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="T22" s="56"/>
+      <c r="T22" s="56">
+        <v>15.1</v>
+      </c>
       <c r="U22" s="56"/>
       <c r="V22" s="56"/>
       <c r="W22" s="56"/>
@@ -8338,7 +8373,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8411,7 +8446,9 @@
       <c r="S23" s="56">
         <v>27.2</v>
       </c>
-      <c r="T23" s="56"/>
+      <c r="T23" s="56">
+        <v>27.2</v>
+      </c>
       <c r="U23" s="56"/>
       <c r="V23" s="56"/>
       <c r="W23" s="56"/>
@@ -8435,7 +8472,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8508,7 +8545,9 @@
       <c r="S24" s="56">
         <v>32</v>
       </c>
-      <c r="T24" s="56"/>
+      <c r="T24" s="56">
+        <v>31.5</v>
+      </c>
       <c r="U24" s="56"/>
       <c r="V24" s="56"/>
       <c r="W24" s="56"/>
@@ -8532,7 +8571,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8605,7 +8644,9 @@
       <c r="S25" s="56">
         <v>23</v>
       </c>
-      <c r="T25" s="56"/>
+      <c r="T25" s="56">
+        <v>24.8</v>
+      </c>
       <c r="U25" s="56"/>
       <c r="V25" s="56"/>
       <c r="W25" s="56"/>
@@ -8629,7 +8670,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8702,7 +8743,9 @@
       <c r="S26" s="56">
         <v>12.5</v>
       </c>
-      <c r="T26" s="56"/>
+      <c r="T26" s="56">
+        <v>12.6</v>
+      </c>
       <c r="U26" s="56"/>
       <c r="V26" s="56"/>
       <c r="W26" s="56"/>
@@ -8726,7 +8769,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8799,7 +8842,9 @@
       <c r="S27" s="56">
         <v>28.3</v>
       </c>
-      <c r="T27" s="56"/>
+      <c r="T27" s="56">
+        <v>27.1</v>
+      </c>
       <c r="U27" s="56"/>
       <c r="V27" s="56"/>
       <c r="W27" s="56"/>
@@ -8823,7 +8868,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8894,7 +8939,9 @@
       <c r="S28" s="56">
         <v>29.1</v>
       </c>
-      <c r="T28" s="56"/>
+      <c r="T28" s="56">
+        <v>24.1</v>
+      </c>
       <c r="U28" s="56"/>
       <c r="V28" s="56"/>
       <c r="W28" s="56"/>
@@ -8918,7 +8965,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8991,7 +9038,9 @@
       <c r="S29" s="56">
         <v>30.2</v>
       </c>
-      <c r="T29" s="56"/>
+      <c r="T29" s="56">
+        <v>27.7</v>
+      </c>
       <c r="U29" s="56"/>
       <c r="V29" s="56"/>
       <c r="W29" s="56"/>
@@ -9015,7 +9064,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9088,7 +9137,9 @@
       <c r="S30" s="56">
         <v>26.2</v>
       </c>
-      <c r="T30" s="56"/>
+      <c r="T30" s="56">
+        <v>24.9</v>
+      </c>
       <c r="U30" s="56"/>
       <c r="V30" s="56"/>
       <c r="W30" s="56"/>
@@ -9112,7 +9163,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9185,7 +9236,9 @@
       <c r="S31" s="98">
         <v>28.6</v>
       </c>
-      <c r="T31" s="98"/>
+      <c r="T31" s="98">
+        <v>29</v>
+      </c>
       <c r="U31" s="98"/>
       <c r="V31" s="98"/>
       <c r="W31" s="98"/>
@@ -9209,7 +9262,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9282,7 +9335,9 @@
       <c r="S32" s="56">
         <v>20</v>
       </c>
-      <c r="T32" s="56"/>
+      <c r="T32" s="56">
+        <v>20.533333333333331</v>
+      </c>
       <c r="U32" s="56"/>
       <c r="V32" s="56"/>
       <c r="W32" s="56"/>
@@ -9306,7 +9361,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9379,7 +9434,9 @@
       <c r="S33" s="56">
         <v>29.35</v>
       </c>
-      <c r="T33" s="56"/>
+      <c r="T33" s="56">
+        <v>27.2</v>
+      </c>
       <c r="U33" s="56"/>
       <c r="V33" s="56"/>
       <c r="W33" s="56"/>
@@ -9403,7 +9460,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9476,7 +9533,9 @@
       <c r="S34" s="56">
         <v>22.733333333333331</v>
       </c>
-      <c r="T34" s="56"/>
+      <c r="T34" s="56">
+        <v>22</v>
+      </c>
       <c r="U34" s="56"/>
       <c r="V34" s="56"/>
       <c r="W34" s="56"/>
@@ -9500,7 +9559,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9573,7 +9632,9 @@
       <c r="S35" s="56">
         <v>26.35</v>
       </c>
-      <c r="T35" s="56"/>
+      <c r="T35" s="56">
+        <v>25.2</v>
+      </c>
       <c r="U35" s="56"/>
       <c r="V35" s="56"/>
       <c r="W35" s="56"/>
@@ -9597,7 +9658,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9670,7 +9731,9 @@
       <c r="S36" s="56">
         <v>21</v>
       </c>
-      <c r="T36" s="56"/>
+      <c r="T36" s="56">
+        <v>20</v>
+      </c>
       <c r="U36" s="56"/>
       <c r="V36" s="56"/>
       <c r="W36" s="56"/>
@@ -9694,7 +9757,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9767,7 +9830,9 @@
       <c r="S37" s="56">
         <v>28.45</v>
       </c>
-      <c r="T37" s="56"/>
+      <c r="T37" s="56">
+        <v>28.75</v>
+      </c>
       <c r="U37" s="56"/>
       <c r="V37" s="56"/>
       <c r="W37" s="56"/>
@@ -9791,7 +9856,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9864,7 +9929,9 @@
       <c r="S38" s="56">
         <v>15.95</v>
       </c>
-      <c r="T38" s="56"/>
+      <c r="T38" s="56">
+        <v>16.05</v>
+      </c>
       <c r="U38" s="56"/>
       <c r="V38" s="56"/>
       <c r="W38" s="56"/>
@@ -9888,7 +9955,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9961,7 +10028,9 @@
       <c r="S39" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="T39" s="56"/>
+      <c r="T39" s="56">
+        <v>24.13333333333334</v>
+      </c>
       <c r="U39" s="56"/>
       <c r="V39" s="56"/>
       <c r="W39" s="56"/>
@@ -9985,7 +10054,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10056,7 +10125,9 @@
         <v>26.13333333333334</v>
       </c>
       <c r="S40" s="56"/>
-      <c r="T40" s="56"/>
+      <c r="T40" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="U40" s="56"/>
       <c r="V40" s="56"/>
       <c r="W40" s="56"/>
@@ -10080,7 +10151,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10153,7 +10224,9 @@
       <c r="S41" s="56">
         <v>21.933333333333341</v>
       </c>
-      <c r="T41" s="56"/>
+      <c r="T41" s="56">
+        <v>19.133333333333329</v>
+      </c>
       <c r="U41" s="56"/>
       <c r="V41" s="56"/>
       <c r="W41" s="56"/>
@@ -10177,7 +10250,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10250,7 +10323,9 @@
       <c r="S42" s="56">
         <v>28.8</v>
       </c>
-      <c r="T42" s="56"/>
+      <c r="T42" s="56">
+        <v>27.5</v>
+      </c>
       <c r="U42" s="56"/>
       <c r="V42" s="56"/>
       <c r="W42" s="56"/>
@@ -10274,7 +10349,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10347,7 +10422,9 @@
       <c r="S43" s="56">
         <v>31</v>
       </c>
-      <c r="T43" s="56"/>
+      <c r="T43" s="56">
+        <v>28.5</v>
+      </c>
       <c r="U43" s="56"/>
       <c r="V43" s="56"/>
       <c r="W43" s="56"/>
@@ -10371,7 +10448,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10444,7 +10521,9 @@
       <c r="S44" s="56">
         <v>30.425000000000001</v>
       </c>
-      <c r="T44" s="56"/>
+      <c r="T44" s="56">
+        <v>27.75</v>
+      </c>
       <c r="U44" s="56"/>
       <c r="V44" s="56"/>
       <c r="W44" s="56"/>
@@ -10468,7 +10547,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10541,7 +10620,9 @@
       <c r="S45" s="56">
         <v>31</v>
       </c>
-      <c r="T45" s="56"/>
+      <c r="T45" s="56">
+        <v>28.8</v>
+      </c>
       <c r="U45" s="56"/>
       <c r="V45" s="56"/>
       <c r="W45" s="56"/>
@@ -10565,7 +10646,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10638,7 +10719,9 @@
       <c r="S46" s="56">
         <v>29.9</v>
       </c>
-      <c r="T46" s="56"/>
+      <c r="T46" s="56">
+        <v>28.55</v>
+      </c>
       <c r="U46" s="56"/>
       <c r="V46" s="56"/>
       <c r="W46" s="56"/>
@@ -10662,7 +10745,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10735,7 +10818,9 @@
       <c r="S47" s="56">
         <v>31.06666666666667</v>
       </c>
-      <c r="T47" s="56"/>
+      <c r="T47" s="56">
+        <v>28.666666666666671</v>
+      </c>
       <c r="U47" s="56"/>
       <c r="V47" s="56"/>
       <c r="W47" s="56"/>
@@ -10759,7 +10844,7 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ47" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10990,7 +11075,9 @@
       <c r="S50" s="56">
         <v>29.9</v>
       </c>
-      <c r="T50" s="56"/>
+      <c r="T50" s="56">
+        <v>28</v>
+      </c>
       <c r="U50" s="56"/>
       <c r="V50" s="56"/>
       <c r="W50" s="56"/>
@@ -11014,7 +11101,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11245,7 +11332,9 @@
       <c r="S53" s="56">
         <v>30.85</v>
       </c>
-      <c r="T53" s="56"/>
+      <c r="T53" s="56">
+        <v>29.55</v>
+      </c>
       <c r="U53" s="56"/>
       <c r="V53" s="56"/>
       <c r="W53" s="56"/>
@@ -11269,7 +11358,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11342,7 +11431,9 @@
       <c r="S54" s="56">
         <v>31.1</v>
       </c>
-      <c r="T54" s="56"/>
+      <c r="T54" s="56">
+        <v>29.45</v>
+      </c>
       <c r="U54" s="56"/>
       <c r="V54" s="56"/>
       <c r="W54" s="56"/>
@@ -11366,7 +11457,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11435,7 +11526,9 @@
       <c r="S55" s="56">
         <v>31.25</v>
       </c>
-      <c r="T55" s="56"/>
+      <c r="T55" s="56">
+        <v>31.1</v>
+      </c>
       <c r="U55" s="56"/>
       <c r="V55" s="56"/>
       <c r="W55" s="56"/>
@@ -11459,7 +11552,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11769,7 +11862,9 @@
       <c r="S59" s="56">
         <v>29.9</v>
       </c>
-      <c r="T59" s="56"/>
+      <c r="T59" s="56">
+        <v>28.75</v>
+      </c>
       <c r="U59" s="56"/>
       <c r="V59" s="56"/>
       <c r="W59" s="56"/>
@@ -11793,7 +11888,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11862,7 +11957,9 @@
         <v>26.1</v>
       </c>
       <c r="S60" s="56"/>
-      <c r="T60" s="56"/>
+      <c r="T60" s="56">
+        <v>25.35</v>
+      </c>
       <c r="U60" s="56"/>
       <c r="V60" s="56"/>
       <c r="W60" s="56"/>
@@ -11886,7 +11983,7 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ60" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11956,8 +12053,12 @@
       <c r="R61" s="56">
         <v>27.05</v>
       </c>
-      <c r="S61" s="56"/>
-      <c r="T61" s="56"/>
+      <c r="S61" s="56">
+        <v>28.35</v>
+      </c>
+      <c r="T61" s="56">
+        <v>26.5</v>
+      </c>
       <c r="U61" s="56"/>
       <c r="V61" s="56"/>
       <c r="W61" s="56"/>
@@ -11981,7 +12082,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12054,7 +12155,9 @@
       <c r="S62" s="56">
         <v>26.066666666666659</v>
       </c>
-      <c r="T62" s="56"/>
+      <c r="T62" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="U62" s="56"/>
       <c r="V62" s="56"/>
       <c r="W62" s="56"/>
@@ -12078,7 +12181,7 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ62" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12309,7 +12412,9 @@
       <c r="S65" s="56">
         <v>27.1</v>
       </c>
-      <c r="T65" s="56"/>
+      <c r="T65" s="56">
+        <v>23.85</v>
+      </c>
       <c r="U65" s="56"/>
       <c r="V65" s="56"/>
       <c r="W65" s="56"/>
@@ -12333,7 +12438,7 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ65" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12503,7 +12608,9 @@
       <c r="S67" s="56">
         <v>25.375</v>
       </c>
-      <c r="T67" s="56"/>
+      <c r="T67" s="56">
+        <v>26.3</v>
+      </c>
       <c r="U67" s="56"/>
       <c r="V67" s="56"/>
       <c r="W67" s="56"/>
@@ -12527,7 +12634,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12600,7 +12707,9 @@
       <c r="S68" s="56">
         <v>25.15</v>
       </c>
-      <c r="T68" s="56"/>
+      <c r="T68" s="56">
+        <v>26.75</v>
+      </c>
       <c r="U68" s="56"/>
       <c r="V68" s="56"/>
       <c r="W68" s="56"/>
@@ -12624,7 +12733,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12697,7 +12806,9 @@
       <c r="S69" s="56">
         <v>24.95</v>
       </c>
-      <c r="T69" s="56"/>
+      <c r="T69" s="56">
+        <v>24.85</v>
+      </c>
       <c r="U69" s="56"/>
       <c r="V69" s="56"/>
       <c r="W69" s="56"/>
@@ -12721,7 +12832,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -12791,8 +12902,12 @@
       <c r="R70" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="S70" s="56"/>
-      <c r="T70" s="56"/>
+      <c r="S70" s="56">
+        <v>25.533333333333331</v>
+      </c>
+      <c r="T70" s="56">
+        <v>25.466666666666669</v>
+      </c>
       <c r="U70" s="56"/>
       <c r="V70" s="56"/>
       <c r="W70" s="56"/>
@@ -12816,7 +12931,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12885,7 +13000,9 @@
       <c r="S71" s="56">
         <v>27.3</v>
       </c>
-      <c r="T71" s="56"/>
+      <c r="T71" s="56">
+        <v>25.233333333333331</v>
+      </c>
       <c r="U71" s="56"/>
       <c r="V71" s="56"/>
       <c r="W71" s="56"/>
@@ -12909,7 +13026,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12982,7 +13099,9 @@
       <c r="S72" s="56">
         <v>27.166666666666671</v>
       </c>
-      <c r="T72" s="56"/>
+      <c r="T72" s="56">
+        <v>26.3</v>
+      </c>
       <c r="U72" s="56"/>
       <c r="V72" s="56"/>
       <c r="W72" s="56"/>
@@ -13006,7 +13125,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13075,7 +13194,9 @@
       <c r="S73" s="56">
         <v>26.1</v>
       </c>
-      <c r="T73" s="56"/>
+      <c r="T73" s="56">
+        <v>24.3</v>
+      </c>
       <c r="U73" s="56"/>
       <c r="V73" s="56"/>
       <c r="W73" s="56"/>
@@ -13099,7 +13220,7 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ73" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13172,7 +13293,9 @@
       <c r="S74" s="56">
         <v>21.3</v>
       </c>
-      <c r="T74" s="56"/>
+      <c r="T74" s="56">
+        <v>21.55</v>
+      </c>
       <c r="U74" s="56"/>
       <c r="V74" s="56"/>
       <c r="W74" s="56"/>
@@ -13196,7 +13319,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13269,7 +13392,9 @@
       <c r="S75" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="T75" s="56"/>
+      <c r="T75" s="56">
+        <v>20.06666666666667</v>
+      </c>
       <c r="U75" s="56"/>
       <c r="V75" s="56"/>
       <c r="W75" s="56"/>
@@ -13293,7 +13418,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13366,7 +13491,9 @@
       <c r="S76" s="56">
         <v>22.15</v>
       </c>
-      <c r="T76" s="56"/>
+      <c r="T76" s="56">
+        <v>20.7</v>
+      </c>
       <c r="U76" s="56"/>
       <c r="V76" s="56"/>
       <c r="W76" s="56"/>
@@ -13390,7 +13517,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13463,7 +13590,9 @@
       <c r="S77" s="56">
         <v>25.466666666666669</v>
       </c>
-      <c r="T77" s="56"/>
+      <c r="T77" s="56">
+        <v>25.4</v>
+      </c>
       <c r="U77" s="56"/>
       <c r="V77" s="56"/>
       <c r="W77" s="56"/>
@@ -13487,7 +13616,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13555,8 +13684,12 @@
       <c r="R78" s="56">
         <v>33.900000000000013</v>
       </c>
-      <c r="S78" s="56"/>
-      <c r="T78" s="56"/>
+      <c r="S78" s="56">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="T78" s="56">
+        <v>34.049999999999997</v>
+      </c>
       <c r="U78" s="56"/>
       <c r="V78" s="56"/>
       <c r="W78" s="56"/>
@@ -13580,7 +13713,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13653,7 +13786,9 @@
       <c r="S79" s="56">
         <v>33.666666666666657</v>
       </c>
-      <c r="T79" s="56"/>
+      <c r="T79" s="56">
+        <v>33</v>
+      </c>
       <c r="U79" s="56"/>
       <c r="V79" s="56"/>
       <c r="W79" s="56"/>
@@ -13677,7 +13812,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13750,7 +13885,9 @@
       <c r="S80" s="56">
         <v>22.533333333333331</v>
       </c>
-      <c r="T80" s="56"/>
+      <c r="T80" s="56">
+        <v>22.266666666666669</v>
+      </c>
       <c r="U80" s="56"/>
       <c r="V80" s="56"/>
       <c r="W80" s="56"/>
@@ -13774,7 +13911,7 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ80" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13847,7 +13984,9 @@
       <c r="S81" s="56">
         <v>24.4</v>
       </c>
-      <c r="T81" s="56"/>
+      <c r="T81" s="56">
+        <v>26.1</v>
+      </c>
       <c r="U81" s="56"/>
       <c r="V81" s="56"/>
       <c r="W81" s="56"/>
@@ -13871,7 +14010,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13942,7 +14081,9 @@
       <c r="S82" s="56">
         <v>27.066666666666659</v>
       </c>
-      <c r="T82" s="56"/>
+      <c r="T82" s="56">
+        <v>27.266666666666669</v>
+      </c>
       <c r="U82" s="56"/>
       <c r="V82" s="56"/>
       <c r="W82" s="56"/>
@@ -13966,7 +14107,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14197,7 +14338,9 @@
       <c r="S85" s="56">
         <v>32.1</v>
       </c>
-      <c r="T85" s="56"/>
+      <c r="T85" s="56">
+        <v>33.049999999999997</v>
+      </c>
       <c r="U85" s="56"/>
       <c r="V85" s="56"/>
       <c r="W85" s="56"/>
@@ -14221,7 +14364,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14294,7 +14437,9 @@
       <c r="S86" s="56">
         <v>30.35</v>
       </c>
-      <c r="T86" s="56"/>
+      <c r="T86" s="56">
+        <v>30.7</v>
+      </c>
       <c r="U86" s="56"/>
       <c r="V86" s="56"/>
       <c r="W86" s="56"/>
@@ -14318,7 +14463,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14391,7 +14536,9 @@
       <c r="S87" s="56">
         <v>32.75</v>
       </c>
-      <c r="T87" s="56"/>
+      <c r="T87" s="56">
+        <v>31.75</v>
+      </c>
       <c r="U87" s="56"/>
       <c r="V87" s="56"/>
       <c r="W87" s="56"/>
@@ -14415,7 +14562,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14488,7 +14635,9 @@
       <c r="S88" s="56">
         <v>32</v>
       </c>
-      <c r="T88" s="56"/>
+      <c r="T88" s="56">
+        <v>30.2</v>
+      </c>
       <c r="U88" s="56"/>
       <c r="V88" s="56"/>
       <c r="W88" s="56"/>
@@ -14512,7 +14661,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14583,7 +14732,9 @@
       <c r="S89" s="56">
         <v>34.549999999999997</v>
       </c>
-      <c r="T89" s="56"/>
+      <c r="T89" s="56">
+        <v>32.35</v>
+      </c>
       <c r="U89" s="56"/>
       <c r="V89" s="56"/>
       <c r="W89" s="56"/>
@@ -14607,7 +14758,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14680,7 +14831,9 @@
       <c r="S90" s="56">
         <v>33.950000000000003</v>
       </c>
-      <c r="T90" s="56"/>
+      <c r="T90" s="56">
+        <v>32.15</v>
+      </c>
       <c r="U90" s="56"/>
       <c r="V90" s="56"/>
       <c r="W90" s="56"/>
@@ -14704,7 +14857,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14771,7 +14924,9 @@
       <c r="S91" s="56">
         <v>34</v>
       </c>
-      <c r="T91" s="56"/>
+      <c r="T91" s="56">
+        <v>33.1</v>
+      </c>
       <c r="U91" s="56"/>
       <c r="V91" s="56"/>
       <c r="W91" s="56"/>
@@ -14795,7 +14950,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14868,7 +15023,9 @@
       <c r="S92" s="56">
         <v>19.100000000000001</v>
       </c>
-      <c r="T92" s="56"/>
+      <c r="T92" s="56">
+        <v>19.149999999999999</v>
+      </c>
       <c r="U92" s="56"/>
       <c r="V92" s="56"/>
       <c r="W92" s="56"/>
@@ -14892,7 +15049,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14965,7 +15122,9 @@
       <c r="S93" s="56">
         <v>25.266666666666669</v>
       </c>
-      <c r="T93" s="56"/>
+      <c r="T93" s="56">
+        <v>25.466666666666669</v>
+      </c>
       <c r="U93" s="56"/>
       <c r="V93" s="56"/>
       <c r="W93" s="56"/>
@@ -14989,7 +15148,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15056,7 +15215,9 @@
       <c r="S94" s="56">
         <v>17.75</v>
       </c>
-      <c r="T94" s="56"/>
+      <c r="T94" s="56">
+        <v>17.100000000000001</v>
+      </c>
       <c r="U94" s="56"/>
       <c r="V94" s="56"/>
       <c r="W94" s="56"/>
@@ -15080,7 +15241,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15153,7 +15314,9 @@
       <c r="S95" s="56">
         <v>15.65</v>
       </c>
-      <c r="T95" s="56"/>
+      <c r="T95" s="56">
+        <v>14.55</v>
+      </c>
       <c r="U95" s="56"/>
       <c r="V95" s="56"/>
       <c r="W95" s="56"/>
@@ -15177,7 +15340,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15329,7 +15492,9 @@
       <c r="S97" s="56">
         <v>18.333333333333329</v>
       </c>
-      <c r="T97" s="56"/>
+      <c r="T97" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="U97" s="56"/>
       <c r="V97" s="56"/>
       <c r="W97" s="56"/>
@@ -15353,7 +15518,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15426,7 +15591,9 @@
       <c r="S98" s="56">
         <v>14.35</v>
       </c>
-      <c r="T98" s="56"/>
+      <c r="T98" s="56">
+        <v>14.2</v>
+      </c>
       <c r="U98" s="56"/>
       <c r="V98" s="56"/>
       <c r="W98" s="56"/>
@@ -15450,7 +15617,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15523,7 +15690,9 @@
       <c r="S99" s="56">
         <v>16.233333333333331</v>
       </c>
-      <c r="T99" s="56"/>
+      <c r="T99" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="U99" s="56"/>
       <c r="V99" s="56"/>
       <c r="W99" s="56"/>
@@ -15547,7 +15716,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15620,7 +15789,9 @@
       <c r="S100" s="56">
         <v>17.666666666666671</v>
       </c>
-      <c r="T100" s="56"/>
+      <c r="T100" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="U100" s="56"/>
       <c r="V100" s="56"/>
       <c r="W100" s="56"/>
@@ -15644,7 +15815,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15717,7 +15888,9 @@
       <c r="S101" s="56">
         <v>14.45</v>
       </c>
-      <c r="T101" s="56"/>
+      <c r="T101" s="56">
+        <v>14.25</v>
+      </c>
       <c r="U101" s="56"/>
       <c r="V101" s="56"/>
       <c r="W101" s="56"/>
@@ -15741,7 +15914,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15802,7 +15975,9 @@
       <c r="S102" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="T102" s="56"/>
+      <c r="T102" s="56">
+        <v>13.2</v>
+      </c>
       <c r="U102" s="56"/>
       <c r="V102" s="56"/>
       <c r="W102" s="56"/>
@@ -15826,7 +16001,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16057,7 +16232,9 @@
       <c r="S105" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="T105" s="56"/>
+      <c r="T105" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="U105" s="56"/>
       <c r="V105" s="56"/>
       <c r="W105" s="56"/>
@@ -16081,7 +16258,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16314,7 +16491,9 @@
       <c r="S108" s="56">
         <v>14</v>
       </c>
-      <c r="T108" s="56"/>
+      <c r="T108" s="56">
+        <v>15.2</v>
+      </c>
       <c r="U108" s="56"/>
       <c r="V108" s="56"/>
       <c r="W108" s="56"/>
@@ -16338,7 +16517,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16411,7 +16590,9 @@
       <c r="S109" s="56">
         <v>15.8</v>
       </c>
-      <c r="T109" s="56"/>
+      <c r="T109" s="56">
+        <v>14.45</v>
+      </c>
       <c r="U109" s="56"/>
       <c r="V109" s="56"/>
       <c r="W109" s="56"/>
@@ -16435,7 +16616,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16502,7 +16683,9 @@
       <c r="S110" s="56">
         <v>18</v>
       </c>
-      <c r="T110" s="56"/>
+      <c r="T110" s="56">
+        <v>17.13333333333334</v>
+      </c>
       <c r="U110" s="56"/>
       <c r="V110" s="56"/>
       <c r="W110" s="56"/>
@@ -16526,7 +16709,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16599,7 +16782,9 @@
       <c r="S111" s="56">
         <v>17</v>
       </c>
-      <c r="T111" s="56"/>
+      <c r="T111" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="U111" s="56"/>
       <c r="V111" s="56"/>
       <c r="W111" s="56"/>
@@ -16623,7 +16808,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16696,7 +16881,9 @@
       <c r="S112" s="56">
         <v>18.466666666666669</v>
       </c>
-      <c r="T112" s="56"/>
+      <c r="T112" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="U112" s="56"/>
       <c r="V112" s="56"/>
       <c r="W112" s="56"/>
@@ -16720,7 +16907,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16878,7 +17065,9 @@
       <c r="S114" s="56">
         <v>22.533333333333331</v>
       </c>
-      <c r="T114" s="56"/>
+      <c r="T114" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="U114" s="56"/>
       <c r="V114" s="56"/>
       <c r="W114" s="56"/>
@@ -16902,7 +17091,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16975,7 +17164,9 @@
       <c r="S115" s="56">
         <v>27.1</v>
       </c>
-      <c r="T115" s="56"/>
+      <c r="T115" s="56">
+        <v>26.15</v>
+      </c>
       <c r="U115" s="56"/>
       <c r="V115" s="56"/>
       <c r="W115" s="56"/>
@@ -16999,7 +17190,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17072,7 +17263,9 @@
       <c r="S116" s="56">
         <v>18.93333333333333</v>
       </c>
-      <c r="T116" s="56"/>
+      <c r="T116" s="56">
+        <v>19.2</v>
+      </c>
       <c r="U116" s="56"/>
       <c r="V116" s="56"/>
       <c r="W116" s="56"/>
@@ -17096,7 +17289,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17169,7 +17362,9 @@
       <c r="S117" s="56">
         <v>27</v>
       </c>
-      <c r="T117" s="56"/>
+      <c r="T117" s="56">
+        <v>25.6</v>
+      </c>
       <c r="U117" s="56"/>
       <c r="V117" s="56"/>
       <c r="W117" s="56"/>
@@ -17193,7 +17388,7 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ117" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17256,7 +17451,9 @@
       <c r="S118" s="56">
         <v>30.8</v>
       </c>
-      <c r="T118" s="56"/>
+      <c r="T118" s="56">
+        <v>29.4</v>
+      </c>
       <c r="U118" s="56"/>
       <c r="V118" s="56"/>
       <c r="W118" s="56"/>
@@ -17280,7 +17477,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17616,7 +17813,9 @@
       <c r="S122" s="56">
         <v>13.066666666666659</v>
       </c>
-      <c r="T122" s="56"/>
+      <c r="T122" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="U122" s="56"/>
       <c r="V122" s="56"/>
       <c r="W122" s="56"/>
@@ -17640,7 +17839,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17792,7 +17991,9 @@
       <c r="S124" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="T124" s="56"/>
+      <c r="T124" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="U124" s="56"/>
       <c r="V124" s="56"/>
       <c r="W124" s="56"/>
@@ -17816,7 +18017,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17964,7 +18165,9 @@
       <c r="S126" s="56">
         <v>11.93333333333333</v>
       </c>
-      <c r="T126" s="56"/>
+      <c r="T126" s="56">
+        <v>13</v>
+      </c>
       <c r="U126" s="56"/>
       <c r="V126" s="56"/>
       <c r="W126" s="56"/>
@@ -17988,7 +18191,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18298,7 +18501,9 @@
       <c r="S130" s="56">
         <v>17.733333333333331</v>
       </c>
-      <c r="T130" s="56"/>
+      <c r="T130" s="56">
+        <v>16.8</v>
+      </c>
       <c r="U130" s="56"/>
       <c r="V130" s="56"/>
       <c r="W130" s="56"/>
@@ -18322,7 +18527,7 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ130" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18395,7 +18600,9 @@
       <c r="S131" s="56">
         <v>18.55</v>
       </c>
-      <c r="T131" s="56"/>
+      <c r="T131" s="56">
+        <v>19</v>
+      </c>
       <c r="U131" s="56"/>
       <c r="V131" s="56"/>
       <c r="W131" s="56"/>
@@ -18419,7 +18626,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18568,8 +18775,12 @@
       <c r="R133" s="56">
         <v>13.633333333333329</v>
       </c>
-      <c r="S133" s="56"/>
-      <c r="T133" s="56"/>
+      <c r="S133" s="56">
+        <v>13.16666666666667</v>
+      </c>
+      <c r="T133" s="56">
+        <v>14.53333333333333</v>
+      </c>
       <c r="U133" s="56"/>
       <c r="V133" s="56"/>
       <c r="W133" s="56"/>
@@ -18593,7 +18804,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -18663,8 +18874,12 @@
       <c r="R134" s="56">
         <v>18.2</v>
       </c>
-      <c r="S134" s="56"/>
-      <c r="T134" s="56"/>
+      <c r="S134" s="56">
+        <v>19.666666666666671</v>
+      </c>
+      <c r="T134" s="56">
+        <v>18.466666666666669</v>
+      </c>
       <c r="U134" s="56"/>
       <c r="V134" s="56"/>
       <c r="W134" s="56"/>
@@ -18688,7 +18903,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18761,7 +18976,9 @@
       <c r="S135" s="56">
         <v>22.6</v>
       </c>
-      <c r="T135" s="56"/>
+      <c r="T135" s="56">
+        <v>20.2</v>
+      </c>
       <c r="U135" s="56"/>
       <c r="V135" s="56"/>
       <c r="W135" s="56"/>
@@ -18785,7 +19002,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18858,7 +19075,9 @@
       <c r="S136" s="56">
         <v>11.33333333333333</v>
       </c>
-      <c r="T136" s="56"/>
+      <c r="T136" s="56">
+        <v>11.6</v>
+      </c>
       <c r="U136" s="56"/>
       <c r="V136" s="56"/>
       <c r="W136" s="56"/>
@@ -18882,7 +19101,7 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ136" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19034,7 +19253,9 @@
       <c r="S138" s="56">
         <v>23.733333333333331</v>
       </c>
-      <c r="T138" s="56"/>
+      <c r="T138" s="56">
+        <v>23.466666666666669</v>
+      </c>
       <c r="U138" s="56"/>
       <c r="V138" s="56"/>
       <c r="W138" s="56"/>
@@ -19058,7 +19279,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19125,7 +19346,9 @@
       <c r="S139" s="56">
         <v>14</v>
       </c>
-      <c r="T139" s="56"/>
+      <c r="T139" s="56">
+        <v>14.85</v>
+      </c>
       <c r="U139" s="56"/>
       <c r="V139" s="56"/>
       <c r="W139" s="56"/>
@@ -19149,7 +19372,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19222,7 +19445,9 @@
       <c r="S140" s="56">
         <v>16.55</v>
       </c>
-      <c r="T140" s="56"/>
+      <c r="T140" s="56">
+        <v>16.05</v>
+      </c>
       <c r="U140" s="56"/>
       <c r="V140" s="56"/>
       <c r="W140" s="56"/>
@@ -19246,7 +19471,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19319,7 +19544,9 @@
       <c r="S141" s="56">
         <v>13.53333333333333</v>
       </c>
-      <c r="T141" s="56"/>
+      <c r="T141" s="56">
+        <v>14.733333333333331</v>
+      </c>
       <c r="U141" s="56"/>
       <c r="V141" s="56"/>
       <c r="W141" s="56"/>
@@ -19343,7 +19570,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19416,7 +19643,9 @@
       <c r="S142" s="56">
         <v>12</v>
       </c>
-      <c r="T142" s="56"/>
+      <c r="T142" s="56">
+        <v>11.55</v>
+      </c>
       <c r="U142" s="56"/>
       <c r="V142" s="56"/>
       <c r="W142" s="56"/>
@@ -19440,7 +19669,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19513,7 +19742,9 @@
       <c r="S143" s="56">
         <v>28.666666666666671</v>
       </c>
-      <c r="T143" s="56"/>
+      <c r="T143" s="56">
+        <v>28.333333333333329</v>
+      </c>
       <c r="U143" s="56"/>
       <c r="V143" s="56"/>
       <c r="W143" s="56"/>
@@ -19537,7 +19768,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19610,7 +19841,9 @@
       <c r="S144" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="T144" s="56"/>
+      <c r="T144" s="56">
+        <v>15.53333333333333</v>
+      </c>
       <c r="U144" s="56"/>
       <c r="V144" s="56"/>
       <c r="W144" s="56"/>
@@ -19634,7 +19867,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19707,7 +19940,9 @@
       <c r="S145" s="56">
         <v>20.333333333333329</v>
       </c>
-      <c r="T145" s="56"/>
+      <c r="T145" s="56">
+        <v>20.6</v>
+      </c>
       <c r="U145" s="56"/>
       <c r="V145" s="56"/>
       <c r="W145" s="56"/>
@@ -19731,7 +19966,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19901,7 +20136,9 @@
       <c r="S147" s="56">
         <v>27.333333333333329</v>
       </c>
-      <c r="T147" s="56"/>
+      <c r="T147" s="56">
+        <v>26.066666666666659</v>
+      </c>
       <c r="U147" s="56"/>
       <c r="V147" s="56"/>
       <c r="W147" s="56"/>
@@ -19925,7 +20162,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19998,7 +20235,9 @@
       <c r="S148" s="56">
         <v>30.6</v>
       </c>
-      <c r="T148" s="56"/>
+      <c r="T148" s="56">
+        <v>30.13333333333334</v>
+      </c>
       <c r="U148" s="56"/>
       <c r="V148" s="56"/>
       <c r="W148" s="56"/>
@@ -20022,7 +20261,7 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ148" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20095,7 +20334,9 @@
       <c r="S149" s="56">
         <v>24.93333333333333</v>
       </c>
-      <c r="T149" s="56"/>
+      <c r="T149" s="56">
+        <v>24.4</v>
+      </c>
       <c r="U149" s="56"/>
       <c r="V149" s="56"/>
       <c r="W149" s="56"/>
@@ -20119,7 +20360,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20271,7 +20512,9 @@
       <c r="S151" s="56">
         <v>24</v>
       </c>
-      <c r="T151" s="56"/>
+      <c r="T151" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="U151" s="56"/>
       <c r="V151" s="56"/>
       <c r="W151" s="56"/>
@@ -20295,7 +20538,7 @@
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ151" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20619,7 +20862,9 @@
       <c r="S155" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="T155" s="56"/>
+      <c r="T155" s="56">
+        <v>29.4</v>
+      </c>
       <c r="U155" s="56"/>
       <c r="V155" s="56"/>
       <c r="W155" s="56"/>
@@ -20643,7 +20888,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20793,7 +21038,9 @@
       <c r="S157" s="56">
         <v>32.733333333333327</v>
       </c>
-      <c r="T157" s="56"/>
+      <c r="T157" s="56">
+        <v>31.533333333333331</v>
+      </c>
       <c r="U157" s="56"/>
       <c r="V157" s="56"/>
       <c r="W157" s="56"/>
@@ -20817,7 +21064,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20890,7 +21137,9 @@
       <c r="S158" s="56">
         <v>31.6</v>
       </c>
-      <c r="T158" s="56"/>
+      <c r="T158" s="56">
+        <v>32.06666666666667</v>
+      </c>
       <c r="U158" s="56"/>
       <c r="V158" s="56"/>
       <c r="W158" s="56"/>
@@ -20914,7 +21163,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20987,7 +21236,9 @@
       <c r="S159" s="56">
         <v>22.333333333333329</v>
       </c>
-      <c r="T159" s="56"/>
+      <c r="T159" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="U159" s="56"/>
       <c r="V159" s="56"/>
       <c r="W159" s="56"/>
@@ -21011,7 +21262,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21082,7 +21333,9 @@
       <c r="S160" s="56">
         <v>28.266666666666669</v>
       </c>
-      <c r="T160" s="56"/>
+      <c r="T160" s="56">
+        <v>27.533333333333331</v>
+      </c>
       <c r="U160" s="56"/>
       <c r="V160" s="56"/>
       <c r="W160" s="56"/>
@@ -21106,7 +21359,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21258,7 +21511,9 @@
       <c r="S162" s="56">
         <v>29.733333333333331</v>
       </c>
-      <c r="T162" s="56"/>
+      <c r="T162" s="56">
+        <v>28.8</v>
+      </c>
       <c r="U162" s="56"/>
       <c r="V162" s="56"/>
       <c r="W162" s="56"/>
@@ -21282,7 +21537,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21355,7 +21610,9 @@
       <c r="S163" s="56">
         <v>21.933333333333341</v>
       </c>
-      <c r="T163" s="56"/>
+      <c r="T163" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="U163" s="56"/>
       <c r="V163" s="56"/>
       <c r="W163" s="56"/>
@@ -21379,7 +21636,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21452,7 +21709,9 @@
       <c r="S164" s="56">
         <v>26.55</v>
       </c>
-      <c r="T164" s="56"/>
+      <c r="T164" s="56">
+        <v>25.75</v>
+      </c>
       <c r="U164" s="56"/>
       <c r="V164" s="56"/>
       <c r="W164" s="56"/>
@@ -21476,7 +21735,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21628,7 +21887,9 @@
       <c r="S166" s="56">
         <v>15.8</v>
       </c>
-      <c r="T166" s="56"/>
+      <c r="T166" s="56">
+        <v>14.93333333333333</v>
+      </c>
       <c r="U166" s="56"/>
       <c r="V166" s="56"/>
       <c r="W166" s="56"/>
@@ -21652,7 +21913,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21725,7 +21986,9 @@
       <c r="S167" s="56">
         <v>23.06666666666667</v>
       </c>
-      <c r="T167" s="56"/>
+      <c r="T167" s="56">
+        <v>21.933333333333341</v>
+      </c>
       <c r="U167" s="56"/>
       <c r="V167" s="56"/>
       <c r="W167" s="56"/>
@@ -21749,7 +22012,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21822,7 +22085,9 @@
       <c r="S168" s="56">
         <v>30.5</v>
       </c>
-      <c r="T168" s="56"/>
+      <c r="T168" s="56">
+        <v>27.55</v>
+      </c>
       <c r="U168" s="56"/>
       <c r="V168" s="56"/>
       <c r="W168" s="56"/>
@@ -21846,7 +22111,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21919,7 +22184,9 @@
       <c r="S169" s="56">
         <v>9.25</v>
       </c>
-      <c r="T169" s="56"/>
+      <c r="T169" s="56">
+        <v>9.6000000000000014</v>
+      </c>
       <c r="U169" s="56"/>
       <c r="V169" s="56"/>
       <c r="W169" s="56"/>
@@ -21943,7 +22210,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22016,7 +22283,9 @@
       <c r="S170" s="56">
         <v>26.93333333333333</v>
       </c>
-      <c r="T170" s="56"/>
+      <c r="T170" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="U170" s="56"/>
       <c r="V170" s="56"/>
       <c r="W170" s="56"/>
@@ -22040,7 +22309,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22104,8 +22373,12 @@
       <c r="R171" s="56">
         <v>22.86666666666666</v>
       </c>
-      <c r="S171" s="56"/>
-      <c r="T171" s="56"/>
+      <c r="S171" s="56">
+        <v>22.13333333333334</v>
+      </c>
+      <c r="T171" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="U171" s="56"/>
       <c r="V171" s="56"/>
       <c r="W171" s="56"/>
@@ -22129,7 +22402,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22202,7 +22475,9 @@
       <c r="S172" s="56">
         <v>26.6</v>
       </c>
-      <c r="T172" s="56"/>
+      <c r="T172" s="56">
+        <v>25.95</v>
+      </c>
       <c r="U172" s="56"/>
       <c r="V172" s="56"/>
       <c r="W172" s="56"/>
@@ -22226,7 +22501,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22299,7 +22574,9 @@
       <c r="S173" s="56">
         <v>26.05</v>
       </c>
-      <c r="T173" s="56"/>
+      <c r="T173" s="56">
+        <v>26.15</v>
+      </c>
       <c r="U173" s="56"/>
       <c r="V173" s="56"/>
       <c r="W173" s="56"/>
@@ -22323,7 +22600,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22477,7 +22754,9 @@
       <c r="Q175" s="56"/>
       <c r="R175" s="56"/>
       <c r="S175" s="56"/>
-      <c r="T175" s="56"/>
+      <c r="T175" s="56">
+        <v>25.6</v>
+      </c>
       <c r="U175" s="56"/>
       <c r="V175" s="56"/>
       <c r="W175" s="56"/>
@@ -22501,7 +22780,7 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ175" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22732,7 +23011,9 @@
       <c r="S178" s="56">
         <v>24.8</v>
       </c>
-      <c r="T178" s="56"/>
+      <c r="T178" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="U178" s="56"/>
       <c r="V178" s="56"/>
       <c r="W178" s="56"/>
@@ -22756,7 +23037,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22829,7 +23110,9 @@
       <c r="S179" s="56">
         <v>18.649999999999999</v>
       </c>
-      <c r="T179" s="56"/>
+      <c r="T179" s="56">
+        <v>18.45</v>
+      </c>
       <c r="U179" s="56"/>
       <c r="V179" s="56"/>
       <c r="W179" s="56"/>
@@ -22853,7 +23136,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23005,7 +23288,9 @@
       <c r="S181" s="56">
         <v>32.933333333333337</v>
       </c>
-      <c r="T181" s="56"/>
+      <c r="T181" s="56">
+        <v>34</v>
+      </c>
       <c r="U181" s="56"/>
       <c r="V181" s="56"/>
       <c r="W181" s="56"/>
@@ -23029,7 +23314,7 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ181" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23260,7 +23545,9 @@
       <c r="S184" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="T184" s="56"/>
+      <c r="T184" s="56">
+        <v>28.733333333333331</v>
+      </c>
       <c r="U184" s="56"/>
       <c r="V184" s="56"/>
       <c r="W184" s="56"/>
@@ -23284,7 +23571,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23353,7 +23640,9 @@
       <c r="S185" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="T185" s="56"/>
+      <c r="T185" s="56">
+        <v>31.266666666666669</v>
+      </c>
       <c r="U185" s="56"/>
       <c r="V185" s="56"/>
       <c r="W185" s="56"/>
@@ -23377,7 +23666,7 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ185" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23796,7 +24085,9 @@
       <c r="S190" s="56">
         <v>30.4</v>
       </c>
-      <c r="T190" s="56"/>
+      <c r="T190" s="56">
+        <v>32.133333333333333</v>
+      </c>
       <c r="U190" s="56"/>
       <c r="V190" s="56"/>
       <c r="W190" s="56"/>
@@ -23820,7 +24111,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23893,7 +24184,9 @@
       <c r="S191" s="56">
         <v>19.649999999999999</v>
       </c>
-      <c r="T191" s="56"/>
+      <c r="T191" s="56">
+        <v>20.7</v>
+      </c>
       <c r="U191" s="56"/>
       <c r="V191" s="56"/>
       <c r="W191" s="56"/>
@@ -23917,7 +24210,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23990,7 +24283,9 @@
       <c r="S192" s="56">
         <v>26.8</v>
       </c>
-      <c r="T192" s="56"/>
+      <c r="T192" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="U192" s="56"/>
       <c r="V192" s="56"/>
       <c r="W192" s="56"/>
@@ -24014,7 +24309,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24087,7 +24382,9 @@
       <c r="S193" s="56">
         <v>30</v>
       </c>
-      <c r="T193" s="56"/>
+      <c r="T193" s="56">
+        <v>30.75</v>
+      </c>
       <c r="U193" s="56"/>
       <c r="V193" s="56"/>
       <c r="W193" s="56"/>
@@ -24111,7 +24408,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24184,7 +24481,9 @@
       <c r="S194" s="56">
         <v>24.13333333333334</v>
       </c>
-      <c r="T194" s="56"/>
+      <c r="T194" s="56">
+        <v>23.2</v>
+      </c>
       <c r="U194" s="56"/>
       <c r="V194" s="56"/>
       <c r="W194" s="56"/>
@@ -24208,7 +24507,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24277,7 +24576,9 @@
       <c r="S195" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="T195" s="56"/>
+      <c r="T195" s="56">
+        <v>30.6</v>
+      </c>
       <c r="U195" s="56"/>
       <c r="V195" s="56"/>
       <c r="W195" s="56"/>
@@ -24301,7 +24602,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24374,7 +24675,9 @@
       <c r="S196" s="56">
         <v>24.86666666666666</v>
       </c>
-      <c r="T196" s="56"/>
+      <c r="T196" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="U196" s="56"/>
       <c r="V196" s="56"/>
       <c r="W196" s="56"/>
@@ -24398,7 +24701,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24471,7 +24774,9 @@
       <c r="S197" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="T197" s="56"/>
+      <c r="T197" s="56">
+        <v>29.2</v>
+      </c>
       <c r="U197" s="56"/>
       <c r="V197" s="56"/>
       <c r="W197" s="56"/>
@@ -24495,7 +24800,7 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ197" s="71" t="str">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
@@ -24568,7 +24873,9 @@
       <c r="S198" s="56">
         <v>23.4</v>
       </c>
-      <c r="T198" s="56"/>
+      <c r="T198" s="56">
+        <v>23.55</v>
+      </c>
       <c r="U198" s="56"/>
       <c r="V198" s="56"/>
       <c r="W198" s="56"/>
@@ -24592,7 +24899,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24665,7 +24972,9 @@
       <c r="S199" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="T199" s="56"/>
+      <c r="T199" s="56">
+        <v>16.93333333333333</v>
+      </c>
       <c r="U199" s="56"/>
       <c r="V199" s="56"/>
       <c r="W199" s="56"/>
@@ -24689,7 +24998,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24760,7 +25069,9 @@
       <c r="S200" s="56">
         <v>14.95</v>
       </c>
-      <c r="T200" s="56"/>
+      <c r="T200" s="56">
+        <v>15.45</v>
+      </c>
       <c r="U200" s="56"/>
       <c r="V200" s="56"/>
       <c r="W200" s="56"/>
@@ -24784,7 +25095,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24857,7 +25168,9 @@
       <c r="S201" s="56">
         <v>29.85</v>
       </c>
-      <c r="T201" s="56"/>
+      <c r="T201" s="56">
+        <v>30.4</v>
+      </c>
       <c r="U201" s="56"/>
       <c r="V201" s="56"/>
       <c r="W201" s="56"/>
@@ -24881,7 +25194,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24952,7 +25265,9 @@
       <c r="S202" s="56">
         <v>13.35</v>
       </c>
-      <c r="T202" s="56"/>
+      <c r="T202" s="56">
+        <v>12.95</v>
+      </c>
       <c r="U202" s="56"/>
       <c r="V202" s="56"/>
       <c r="W202" s="56"/>
@@ -24976,7 +25291,7 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ202" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25222,7 +25537,9 @@
       <c r="R205" s="56">
         <v>15.85</v>
       </c>
-      <c r="S205" s="56"/>
+      <c r="S205" s="56">
+        <v>16.3</v>
+      </c>
       <c r="T205" s="56"/>
       <c r="U205" s="56"/>
       <c r="V205" s="56"/>
@@ -25247,7 +25564,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25320,7 +25637,9 @@
       <c r="S206" s="56">
         <v>15.2</v>
       </c>
-      <c r="T206" s="56"/>
+      <c r="T206" s="56">
+        <v>13.4</v>
+      </c>
       <c r="U206" s="56"/>
       <c r="V206" s="56"/>
       <c r="W206" s="56"/>
@@ -25344,7 +25663,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25415,7 +25734,9 @@
       <c r="S207" s="56">
         <v>13.93333333333333</v>
       </c>
-      <c r="T207" s="56"/>
+      <c r="T207" s="56">
+        <v>14</v>
+      </c>
       <c r="U207" s="56"/>
       <c r="V207" s="56"/>
       <c r="W207" s="56"/>
@@ -25439,7 +25760,7 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ207" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25510,7 +25831,9 @@
       <c r="S208" s="56">
         <v>14.55</v>
       </c>
-      <c r="T208" s="56"/>
+      <c r="T208" s="56">
+        <v>14.75</v>
+      </c>
       <c r="U208" s="56"/>
       <c r="V208" s="56"/>
       <c r="W208" s="56"/>
@@ -25534,7 +25857,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25607,7 +25930,9 @@
       <c r="S209" s="56">
         <v>10.55</v>
       </c>
-      <c r="T209" s="56"/>
+      <c r="T209" s="56">
+        <v>10.9</v>
+      </c>
       <c r="U209" s="56"/>
       <c r="V209" s="56"/>
       <c r="W209" s="56"/>
@@ -25631,7 +25956,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25797,7 +26122,9 @@
       <c r="S211" s="56">
         <v>8</v>
       </c>
-      <c r="T211" s="56"/>
+      <c r="T211" s="56">
+        <v>7.9</v>
+      </c>
       <c r="U211" s="56"/>
       <c r="V211" s="56"/>
       <c r="W211" s="56"/>
@@ -25821,7 +26148,7 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ211" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25894,7 +26221,9 @@
       <c r="S212" s="56">
         <v>29.35</v>
       </c>
-      <c r="T212" s="56"/>
+      <c r="T212" s="56">
+        <v>28.6</v>
+      </c>
       <c r="U212" s="56"/>
       <c r="V212" s="56"/>
       <c r="W212" s="56"/>
@@ -25918,7 +26247,7 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ212" s="71" t="str">
         <f t="shared" si="10"/>
